--- a/web-client/admin/public/templates/cake_import_template.xlsx
+++ b/web-client/admin/public/templates/cake_import_template.xlsx
@@ -4,14 +4,17 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Cakes" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Cakes Import Template" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+  <si>
+    <t>ID Sản phẩm</t>
+  </si>
   <si>
     <t>Tên Bánh</t>
   </si>
@@ -43,35 +46,65 @@
     <t>Số khẩu phần</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>Bánh Kem Dâu Tây</t>
   </si>
   <si>
-    <t>Bánh kem tươi với dâu tây đà lạt</t>
-  </si>
-  <si>
-    <t>https://example.com/dau-tay.jpg</t>
-  </si>
-  <si>
-    <t>Bánh Kem Mousse</t>
-  </si>
-  <si>
-    <t>dâu tây, mousse, sinh nhật</t>
-  </si>
-  <si>
-    <t>Bột mì, trứng, sữa, dâu tây</t>
+    <t>Bánh kem tươi với dâu tây Đà Lạt</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1578985545062-69928b1d9587</t>
+  </si>
+  <si>
+    <t>Bánh Kem</t>
+  </si>
+  <si>
+    <t>cake, strawberry, sweet</t>
+  </si>
+  <si>
+    <t>Bột mì, Trứng, Đường, Dâu tây</t>
+  </si>
+  <si>
+    <t>1kg</t>
+  </si>
+  <si>
+    <t>6-8 người</t>
+  </si>
+  <si>
+    <t>67eca00d98456f7889abcdef</t>
+  </si>
+  <si>
+    <t>[TEST] Bánh Tiramisu Ý</t>
+  </si>
+  <si>
+    <t>Bánh Tiramisu truyền thống Ý với cafe đặc biệt</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1571115177098-24ec4209b5ce</t>
+  </si>
+  <si>
+    <t>Bánh Ngọt</t>
+  </si>
+  <si>
+    <t>tiramisu, coffee</t>
+  </si>
+  <si>
+    <t>Mascarpone, Cafe, Biscoff</t>
   </si>
   <si>
     <t>500g</t>
   </si>
   <si>
-    <t>4-6</t>
+    <t>4 người</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -79,13 +112,22 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4F81BD"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -100,8 +142,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -441,80 +484,122 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="40" customWidth="1"/>
-    <col min="6" max="7" width="25" customWidth="1"/>
-    <col min="8" max="8" width="30" customWidth="1"/>
-    <col min="9" max="10" width="15" customWidth="1"/>
+    <col min="1" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="30" customWidth="1"/>
+    <col min="10" max="11" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2">
+        <v>350000</v>
+      </c>
+      <c r="E2">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2">
-        <v>350000</v>
-      </c>
-      <c r="D2">
-        <v>50</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3">
+        <v>450000</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
